--- a/sheets/대금율보/검수/소양강 처녀.xlsx
+++ b/sheets/대금율보/검수/소양강 처녀.xlsx
@@ -4267,7 +4267,7 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 無潢</t>
         </is>
       </c>
@@ -4352,11 +4352,7 @@
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="26"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="26"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -4367,14 +4363,14 @@
       <c r="I6" s="26"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 汰潕</t>
         </is>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M6" s="26"/>
@@ -4570,7 +4566,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
@@ -4603,13 +4599,13 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-無南‹</t>
+無南</t>
         </is>
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -4640,31 +4636,31 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
-–無</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">면</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">면</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林
+–無</t>
+        </is>
+      </c>
       <c r="K11" s="22"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
@@ -4675,11 +4671,7 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -4699,11 +4691,7 @@
         </is>
       </c>
       <c r="G12" s="23"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="23"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
@@ -4778,7 +4766,7 @@
       <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋湳</t>
         </is>
       </c>
@@ -4797,20 +4785,20 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-南‹</t>
+南</t>
         </is>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-南‹</t>
+南</t>
         </is>
       </c>
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林無</t>
         </is>
       </c>
@@ -5021,7 +5009,7 @@
       <c r="K18" s="26"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 僙黃</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/소양강 처녀.xlsx
+++ b/sheets/대금율보/검수/소양강 처녀.xlsx
@@ -4122,24 +4122,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="M6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="M14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5021,6 +5021,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>